--- a/data/trans_orig/Q5413-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>281515</t>
+          <t>282432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>290869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>328668</t>
+          <t>329011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>339245</t>
+          <t>339320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>616304</t>
+          <t>614346</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>629170</t>
+          <t>628544</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19678</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34149</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187125</t>
+          <t>186136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200956</t>
+          <t>200748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300417</t>
+          <t>301345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>320119</t>
+          <t>320087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>493765</t>
+          <t>493925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>474818</t>
+          <t>472760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>489784</t>
+          <t>489621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634090</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>656918</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1115491</t>
+          <t>1117009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1142066</t>
+          <t>1143491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15829</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>44462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282608</t>
+          <t>281266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>299346</t>
+          <t>299365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,47 +2572,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>334282</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>322944</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>341589</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>91,23%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>334282</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>323754</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>341985</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>91,46%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>613537</t>
+          <t>611337</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>636750</t>
+          <t>636561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45912</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>32037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59245</t>
+          <t>59931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41097</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69986</t>
+          <t>68240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>54414</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>88962</t>
+          <t>89214</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>209801</t>
+          <t>209334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>232443</t>
+          <t>231038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282792</t>
+          <t>283218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317347</t>
+          <t>317622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>504415</t>
+          <t>501134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>543139</t>
+          <t>542646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55221</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88580</t>
+          <t>87175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81131</t>
+          <t>82527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122333</t>
+          <t>122622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499982</t>
+          <t>498251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>527631</t>
+          <t>526582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>614708</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654242</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1123798</t>
+          <t>1126947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1172057</t>
+          <t>1173560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>26165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>315576</t>
+          <t>315427</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>328483</t>
+          <t>328566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>360924</t>
+          <t>361538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>373585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>681676</t>
+          <t>682434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>698866</t>
+          <t>699130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>59763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47250</t>
+          <t>45134</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80671</t>
+          <t>79801</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221848</t>
+          <t>222535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239426</t>
+          <t>239702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>320675</t>
+          <t>317433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>351569</t>
+          <t>353248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550016</t>
+          <t>550805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>587845</t>
+          <t>588093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>40932</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70484</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63388</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543330</t>
+          <t>543780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>565130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683371</t>
+          <t>685580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721578</t>
+          <t>722336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1240059</t>
+          <t>1239897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282610</t>
+          <t>1281715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>360721</t>
+          <t>399228</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>354824</t>
+          <t>393605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>364163</t>
+          <t>403045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>598842</t>
+          <t>428501</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>592218</t>
+          <t>422821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>604715</t>
+          <t>432350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>959564</t>
+          <t>827729</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951084</t>
+          <t>820279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>967918</t>
+          <t>833306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34524</t>
+          <t>35869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58455</t>
+          <t>62997</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48509</t>
+          <t>51509</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70052</t>
+          <t>75457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>80381</t>
+          <t>86693</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68854</t>
+          <t>73922</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92825</t>
+          <t>102261</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>253962</t>
+          <t>279109</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>244205</t>
+          <t>270244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260690</t>
+          <t>286835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>347301</t>
+          <t>380417</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>334911</t>
+          <t>366713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>358380</t>
+          <t>393203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>601263</t>
+          <t>659525</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>586592</t>
+          <t>643481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>613756</t>
+          <t>674487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425358</t>
+          <t>464070</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425358</t>
+          <t>464070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425358</t>
+          <t>464070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707371</t>
+          <t>773381</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707371</t>
+          <t>773381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707371</t>
+          <t>773381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>38927</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65677</t>
+          <t>71194</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>60147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86836</t>
+          <t>85264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57681</t>
+          <t>87805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>119424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>614683</t>
+          <t>678336</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602981</t>
+          <t>667510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>623213</t>
+          <t>687959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>946143</t>
+          <t>808918</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>918959</t>
+          <t>794662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984148</t>
+          <t>821183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1560826</t>
+          <t>1487255</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1536618</t>
+          <t>1469476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1609038</t>
+          <t>1504675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
